--- a/data/contracts.xlsx
+++ b/data/contracts.xlsx
@@ -33,9 +33,6 @@
     <t>Петров Михаил</t>
   </si>
   <si>
-    <t>Terminated</t>
-  </si>
-  <si>
     <t>Сидоров Василий</t>
   </si>
   <si>
@@ -60,9 +57,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:a15="http://schemas.microsoft.com/office/drawing/2012/main" xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:co="http://ncloudtech.com" xmlns:co-ooxml="http://ncloudtech.com/ooxml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/officeDocument/2006/sharedTypes" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main" xmlns:w10="urn:schemas-microsoft-com:office:word" xmlns:w14="http://schemas.microsoft.com/office/word/2010/wordml" xmlns:w15="http://schemas.microsoft.com/office/word/2012/wordml" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:wpg="http://schemas.microsoft.com/office/word/2010/wordprocessingGroup" xmlns:wps="http://schemas.microsoft.com/office/word/2010/wordprocessingShape" xmlns:x="urn:schemas-microsoft-com:office:excel" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" mc:Ignorable="co co-ooxml w14 x14 w15">
   <numFmts>
     <numFmt co:extendedFormatCode="General" formatCode="General" numFmtId="1002"/>
+    <numFmt co:extendedFormatCode="#,##0" formatCode="#,##0" numFmtId="1003"/>
     <numFmt co:extendedFormatCode="General" formatCode="General" numFmtId="1001"/>
     <numFmt co:extendedFormatCode="General" formatCode="General" numFmtId="1000"/>
-    <numFmt co:extendedFormatCode="#,##0" formatCode="#,##0" numFmtId="1003"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -376,7 +373,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46183</v>
+        <v>46548</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>4</v>
@@ -387,18 +384,18 @@
         <v>5</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>46244</v>
+        <v>46255</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row outlineLevel="0" r="4">
-      <c r="A4" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="B4" s="5" t="n">
-        <v>46176</v>
+        <v>46541</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>4</v>
@@ -406,10 +403,10 @@
     </row>
     <row outlineLevel="0" r="5">
       <c r="A5" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>4</v>
@@ -417,21 +414,21 @@
     </row>
     <row outlineLevel="0" r="6">
       <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>46517</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="7">
+      <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="5" t="n">
-        <v>46152</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="7">
-      <c r="A7" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="B7" s="5" t="n">
-        <v>46234</v>
+        <v>46387</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>4</v>
@@ -439,10 +436,10 @@
     </row>
     <row outlineLevel="0" r="8">
       <c r="A8" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>46235</v>
+        <v>46275</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>4</v>
@@ -450,10 +447,10 @@
     </row>
     <row outlineLevel="0" r="9">
       <c r="A9" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>46188</v>
+        <v>46553</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>4</v>
